--- a/output/final/wound/wound distributors (status checked)/status_check_report.xlsx
+++ b/output/final/wound/wound distributors (status checked)/status_check_report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status changes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status changes'!$A$1:$H$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status changes'!$A$1:$H$179</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Status changes'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1687,343 +1687,279 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1">
+    <row r="29" ht="33" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>medical_films_verified_distributors</t>
+          <t>advanced_wound_care_verified_distributors</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Distrupol</t>
+          <t>InterMed Medical</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>distrupol.com</t>
+          <t>https://intermedmedical.com.au</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>Omya</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="9" t="inlineStr"/>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Omya acquired Distrupol in Feb 2025 and retains the Distrupol brand in its operating markets.</t>
+          <t>Same company as 'InterMed Medical Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="30" ht="33" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>medical_films_verified_distributors</t>
+          <t>advanced_wound_care_verified_distributors</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Nexeo Plastics</t>
+          <t>Palex Medical S.A.</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>https://www.nexeoplastics.com</t>
+          <t>palexhealth.com</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>One Rock Capital Partners, LLC</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>One Rock Capital Partners announced that an affiliate completed the acquisition of Nexeo Plastics on March 29, 2019.</t>
+          <t>Same company as 'Palex Medical, S.A. (acquired by Apax Partners)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="31" ht="33" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>medical_films_verified_distributors</t>
+          <t>advanced_wound_care_verified_distributors</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Biesterfeld Polychem S.r.l.</t>
+          <t>Zahrawi Medical</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>biesterfeld.com</t>
+          <t>zahrawigroup.com</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>Biesterfeld SE</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="9" t="inlineStr"/>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Biesterfeld SE acquired 100 percent of the shares in its Italian joint venture Biesterfeld Polychem S.r.l. in July 2026, according to a Biesterfeld Group press release.</t>
+          <t>Same company as 'Zahrawi Group' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1">
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="33" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>medical_films_verified_distributors</t>
+          <t>advanced_wound_care_verified_distributors</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Polymer Direct</t>
+          <t>Creed Medical Limited</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>https://polymerdirect.com.au</t>
+          <t>creedmed.com</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Vinmar International</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Polymer Direct was acquired by Vinmar International on January 1, 2010, according to its PitchBook profile.</t>
+          <t>Same company as 'Creed Medical Ltd' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="33" ht="33" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>medical_films_verified_distributors</t>
+          <t>advanced_wound_care_verified_distributors</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Al Azzaz Chemicals Company</t>
+          <t>Safadifarma S.L.</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>alazzaz.com</t>
+          <t>safadifarma.com</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>Brenntag</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr"/>
+      <c r="F33" s="9" t="inlineStr"/>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Brenntag acquired a 75% majority stake in Al-Azzaz Chemicals Company via a joint venture agreement completed in 2022, according to an official press release by Brenntag.</t>
+          <t>Same company as 'Safadifarma, S.L.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="34" ht="33" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>medical_films_verified_distributors</t>
+          <t>advanced_wound_care_verified_distributors</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Guzman Polymers S.L.</t>
+          <t>HI MEDICAL CO., LTD</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>guztecpolymers.com</t>
+          <t>tradekorea.com</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Hromatka Group</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Guzman Polymers became part of the Hromatka Group in 2020 via the acquisition of a majority stake, as documented on the official Guztec Polymers website.</t>
+          <t>Same company as 'HI MEDICAL CO., LTD.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="35" ht="33" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>medical_films_verified_distributors</t>
+          <t>advanced_wound_care_verified_distributors</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Univar Solutions LLC</t>
+          <t>R.P. Médicas S.A.</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>https://univarsolutions.com</t>
+          <t>https://rpmedicas.com</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>Apollo Global Management</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr"/>
+      <c r="F35" s="9" t="inlineStr"/>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Univar Solutions was acquired by funds managed by affiliates of Apollo Global Management in a buyout transaction completed in 2023, according to an Apollo Global Management press release.</t>
+          <t>Same company as 'RP Médicas' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="36" ht="33" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>medical_films_verified_distributors</t>
+          <t>advanced_wound_care_verified_distributors</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Guztec Polymers (formerly Guzman Polymers)</t>
+          <t>RS Pharma</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>https://guztecpolymers.es</t>
+          <t>https://www.facebook.com/rspharma95</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Hromatka Group</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Austrian polymer distributor Hromatka Group acquired a majority stake in Guzman Polymers in August 2020, which later rebranded to Guztec Polymers.</t>
+          <t>Same company as 'R.S. Pharma' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="33" customHeight="1">
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
           <t>medical_films_verified_distributors</t>
@@ -2031,12 +1967,12 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Guztec Polymers S.L.U. (formerly Guzmán Polímeros)</t>
+          <t>Distrupol</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>guztec.com</t>
+          <t>distrupol.com</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
@@ -2046,17 +1982,17 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Hromatka Group</t>
+          <t>Omya</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Guzmán Polymers became part of the Hromatka Group in 2020 and later rebranded to Guztec Polymers in 2025, according to the company's official LinkedIn profile and website.</t>
+          <t>Omya acquired Distrupol in Feb 2025 and retains the Distrupol brand in its operating markets.</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
@@ -2065,7 +2001,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="24" customHeight="1">
+    <row r="38" ht="33" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>medical_films_verified_distributors</t>
@@ -2073,12 +2009,12 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Guztec Polymers S.r.l.</t>
+          <t>Nexeo Plastics</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>guztecpolymers.it</t>
+          <t>https://www.nexeoplastics.com</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -2088,17 +2024,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Hromatka Group</t>
+          <t>One Rock Capital Partners, LLC</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Guztec Polymers S.r.l. joined the Hromatka Group in mid-2020, as stated on its LinkedIn profile.</t>
+          <t>One Rock Capital Partners announced that an affiliate completed the acquisition of Nexeo Plastics on March 29, 2019.</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -2115,12 +2051,12 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Gamma Chimica S.p.A. (acquired by Stockmeier Group)</t>
+          <t>Biesterfeld Polychem S.r.l.</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>gammachimica.it</t>
+          <t>biesterfeld.com</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
@@ -2130,17 +2066,17 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Stockmeier Group</t>
+          <t>Biesterfeld SE</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>The STOCKMEIER Group acquired a majority shareholding in Gamma Chimica S.p.A. with effect from July 20, 2022, according to Stockmeier's official press release.</t>
+          <t>Biesterfeld SE acquired 100 percent of the shares in its Italian joint venture Biesterfeld Polychem S.r.l. in July 2026, according to a Biesterfeld Group press release.</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
@@ -2149,7 +2085,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="33" customHeight="1">
+    <row r="40" ht="24" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>medical_films_verified_distributors</t>
@@ -2157,12 +2093,12 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Sotac Tecnopolimeri Srl</t>
+          <t>Polymer Direct</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>sotac.it</t>
+          <t>https://polymerdirect.com.au</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2172,17 +2108,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Hromatka</t>
+          <t>Vinmar International</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Sotac Tecnopolimeri Srl was acquired by the Hromatka Group on July 11, 2023, according to a press release on its official website.</t>
+          <t>Polymer Direct was acquired by Vinmar International on January 1, 2010, according to its PitchBook profile.</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -2199,37 +2135,37 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Guzmán Polymers (acquired by Hromatka Group)</t>
+          <t>Al Azzaz Chemicals Company</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>https://guzmanpolymers.com</t>
+          <t>alazzaz.com</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>absorbed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Hromatka Group</t>
+          <t>Brenntag</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>In 2020, Hromatka Group acquired a majority stake in Guzmán Polymers, which later rebranded to Guztec Polymers in 2025 according to a Cluster Envase report.</t>
+          <t>Brenntag acquired a 75% majority stake in Al-Azzaz Chemicals Company via a joint venture agreement completed in 2022, according to an official press release by Brenntag.</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -2241,37 +2177,37 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Velox Spain (acquired by IMCD)</t>
+          <t>Guzman Polymers S.L.</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>https://velox.com</t>
+          <t>guztecpolymers.com</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>absorbed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>IMCD N.V.</t>
+          <t>Hromatka Group</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>IMCD successfully completed the acquisition of 100% of Velox GmbH shares in September 2018 and fully integrated all European operations into IMCD by 2019.</t>
+          <t>Guzman Polymers became part of the Hromatka Group in 2020 via the acquisition of a majority stake, as documented on the official Guztec Polymers website.</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -2283,12 +2219,12 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Campi y Jové (acquired by Ravago Group)</t>
+          <t>Univar Solutions LLC</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>https://campiyjove.com</t>
+          <t>https://univarsolutions.com</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -2298,17 +2234,17 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Ravago Group</t>
+          <t>Apollo Global Management</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Belgian polymer and chemical distribution group Ravago became the full owner of Spanish chemicals distributor Campi y Jové in May 2016, according to Chemical Distributor News.</t>
+          <t>Univar Solutions was acquired by funds managed by affiliates of Apollo Global Management in a buyout transaction completed in 2023, according to an Apollo Global Management press release.</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr">
@@ -2325,12 +2261,12 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Distrupol France</t>
+          <t>Guztec Polymers (formerly Guzman Polymers)</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>distrupol.com</t>
+          <t>https://guztecpolymers.es</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2340,17 +2276,17 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Omya</t>
+          <t>Hromatka Group</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Omya completed the acquisition of Distrupol on February 19, 2025, to establish a global polymers distribution business, while retaining the brand in its operating markets.</t>
+          <t>Austrian polymer distributor Hromatka Group acquired a majority stake in Guzman Polymers in August 2020, which later rebranded to Guztec Polymers.</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -2367,12 +2303,12 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Guzman Polymers France</t>
+          <t>Guztec Polymers S.L.U. (formerly Guzmán Polímeros)</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>guzmanpolymers.com</t>
+          <t>guztec.com</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -2392,7 +2328,7 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Hromatka Group acquired a majority stake in Guzman Polymers in 2020, though the business network continues operating across Europe.</t>
+          <t>Guzmán Polymers became part of the Hromatka Group in 2020 and later rebranded to Guztec Polymers in 2025, according to the company's official LinkedIn profile and website.</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
@@ -2409,12 +2345,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Guzman Polymers, S.L.</t>
+          <t>Guztec Polymers S.r.l.</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>https://guzmanpolymers.es</t>
+          <t>guztecpolymers.it</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2434,7 +2370,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Hromatka Group acquired a majority stake in Guzman Polymers from Guzman Global in August 2020.</t>
+          <t>Guztec Polymers S.r.l. joined the Hromatka Group in mid-2020, as stated on its LinkedIn profile.</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -2443,7 +2379,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="46.5" customHeight="1">
+    <row r="47" ht="33" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
           <t>medical_films_verified_distributors</t>
@@ -2451,12 +2387,12 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Signet Chemical Corporation Pvt. Ltd.</t>
+          <t>Gamma Chimica S.p.A. (acquired by Stockmeier Group)</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>signetchem.com</t>
+          <t>gammachimica.it</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -2466,17 +2402,17 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>IMCD</t>
+          <t>Stockmeier Group</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>IMCD successfully completed the acquisition of a 70% controlling stake in Signet Excipients Private Limited in November 2020, later completing the full acquisition of the remaining 30% shares in 2024 according to IMCD Group announcements.</t>
+          <t>The STOCKMEIER Group acquired a majority shareholding in Gamma Chimica S.p.A. with effect from July 20, 2022, according to Stockmeier's official press release.</t>
         </is>
       </c>
       <c r="H47" s="9" t="inlineStr">
@@ -2493,12 +2429,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>GME Chemicals (S) Pte Ltd</t>
+          <t>Sotac Tecnopolimeri Srl</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>gme-chemicals.com</t>
+          <t>sotac.it</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2508,17 +2444,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Biesterfeld SE</t>
+          <t>Hromatka</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Biesterfeld Group acquired a majority stake in Singapore-based GME Chemicals in 2021, establishing a joint venture with a full takeover planned for 2026.</t>
+          <t>Sotac Tecnopolimeri Srl was acquired by the Hromatka Group on July 11, 2023, according to a press release on its official website.</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -2535,37 +2471,37 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>M. Holland Canada Company</t>
+          <t>Guzmán Polymers (acquired by Hromatka Group)</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>mholland.com</t>
+          <t>https://guzmanpolymers.com</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>absorbed</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>BTMH Holdings LLC</t>
+          <t>Hromatka Group</t>
         </is>
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>According to the Investment Canada Act index, M. Holland Canada Company ULC was acquired by BTMH Holdings LLC in November 2023.</t>
+          <t>In 2020, Hromatka Group acquired a majority stake in Guzmán Polymers, which later rebranded to Guztec Polymers in 2025 according to a Cluster Envase report.</t>
         </is>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -2577,12 +2513,12 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Bamberger Polymers</t>
+          <t>Velox Spain (acquired by IMCD)</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>bambergerpolymers.com</t>
+          <t>https://velox.com</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -2592,17 +2528,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Plastiche SA</t>
+          <t>IMCD N.V.</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Bamberger Polymers merged with Amco Polymers to form Bamberger Amco Polymers in 2024, following its prior acquisition by Plastiche SA, as reported by Plastics News.</t>
+          <t>IMCD successfully completed the acquisition of 100% of Velox GmbH shares in September 2018 and fully integrated all European operations into IMCD by 2019.</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -2611,7 +2547,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1">
+    <row r="51" ht="33" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
           <t>medical_films_verified_distributors</t>
@@ -2619,12 +2555,12 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Polymat</t>
+          <t>Campi y Jové (acquired by Ravago Group)</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>https://www.polymat.com.mx</t>
+          <t>https://campiyjove.com</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -2634,17 +2570,17 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Tricon Energy</t>
+          <t>Ravago Group</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>According to PitchBook, Polymat was acquired by Tricon Energy on December 8, 2023.</t>
+          <t>Belgian polymer and chemical distribution group Ravago became the full owner of Spanish chemicals distributor Campi y Jové in May 2016, according to Chemical Distributor News.</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
@@ -2661,12 +2597,12 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Protea Chemicals</t>
+          <t>Distrupol France</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>proteachemicals.co.za</t>
+          <t>distrupol.com</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -2676,13 +2612,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Omnia Holdings</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr"/>
+          <t>Omya</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Protea Chemicals continues to actively operate as a subsidiary under Omnia Holdings, which acquired the business to form its chemicals division.</t>
+          <t>Omya completed the acquisition of Distrupol on February 19, 2025, to establish a global polymers distribution business, while retaining the brand in its operating markets.</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -2699,12 +2639,12 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>OSP (acquired by Biesterfeld)</t>
+          <t>Guzman Polymers France</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>specialchem.com</t>
+          <t>guzmanpolymers.com</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -2714,17 +2654,17 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Biesterfeld</t>
+          <t>Hromatka Group</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Biesterfeld announced that it acquired a majority stake in South Korean company OSP in May 2026, according to an official press release by Biesterfeld SE.</t>
+          <t>Hromatka Group acquired a majority stake in Guzman Polymers in 2020, though the business network continues operating across Europe.</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
@@ -2733,7 +2673,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="33" customHeight="1">
+    <row r="54" ht="24" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>medical_films_verified_distributors</t>
@@ -2741,12 +2681,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Azelis Korea</t>
+          <t>Guzman Polymers, S.L.</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>azelis.com</t>
+          <t>https://guzmanpolymers.es</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -2756,17 +2696,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Azelis Group</t>
+          <t>Hromatka Group</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>According to the In-Cosmetics Korea directory, Azelis Korea Co., Ltd. was acquired by the Azelis Group in 2018.</t>
+          <t>Hromatka Group acquired a majority stake in Guzman Polymers from Guzman Global in August 2020.</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -2775,7 +2715,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1">
+    <row r="55" ht="46.5" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
           <t>medical_films_verified_distributors</t>
@@ -2783,12 +2723,12 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Signet Excipients Pvt. Ltd. (acquired by IMCD)</t>
+          <t>Signet Chemical Corporation Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>signetexcipients.com</t>
+          <t>signetchem.com</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -2808,7 +2748,7 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>IMCD completed the acquisition of a 70% majority stake in Signet Excipients Pvt. Ltd. in 2020.</t>
+          <t>IMCD successfully completed the acquisition of a 70% controlling stake in Signet Excipients Private Limited in November 2020, later completing the full acquisition of the remaining 30% shares in 2024 according to IMCD Group announcements.</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
@@ -2825,12 +2765,12 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Al-Azzaz Chemicals Company</t>
+          <t>GME Chemicals (S) Pte Ltd</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>https://www.brenntag.com</t>
+          <t>gme-chemicals.com</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2840,17 +2780,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Brenntag</t>
+          <t>Biesterfeld SE</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Brenntag acquired a majority 75% stake in Al-Azzaz Chemicals in 2022, according to an official press release from Brenntag.</t>
+          <t>Biesterfeld Group acquired a majority stake in Singapore-based GME Chemicals in 2021, establishing a joint venture with a full takeover planned for 2026.</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
@@ -2867,22 +2807,22 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>QuantiQ Distribuidora Ltda. (acquired by Caldic)</t>
+          <t>M. Holland Canada Company</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>caldic.com</t>
+          <t>mholland.com</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>absorbed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Caldic</t>
+          <t>BTMH Holdings LLC</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr">
@@ -2892,12 +2832,12 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>QuantiQ officially completed its rebranding and integration into the Caldic brand in January 2023 following Advent International's acquisition structures.</t>
+          <t>According to the Investment Canada Act index, M. Holland Canada Company ULC was acquired by BTMH Holdings LLC in November 2023.</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -2909,22 +2849,22 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Barentz Australia Pty Ltd</t>
+          <t>Bamberger Polymers</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>barentz.com</t>
+          <t>bambergerpolymers.com</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>absorbed</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Barentz</t>
+          <t>Plastiche SA</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -2934,12 +2874,12 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Barentz completed the full acquisition of Additive Solutions (now rebranded as Barentz Australia) in December 2024, according to a press release from Barentz.</t>
+          <t>Bamberger Polymers merged with Amco Polymers to form Bamberger Amco Polymers in 2024, following its prior acquisition by Plastiche SA, as reported by Plastics News.</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -2951,12 +2891,12 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Química Anders</t>
+          <t>Polymat</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>qanders.com</t>
+          <t>https://www.polymat.com.mx</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
@@ -2966,17 +2906,17 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Safic-Alcan</t>
+          <t>Tricon Energy</t>
         </is>
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Safic-Alcan acquired a majority stake in Química Anders in 2025 according to drymix.info.</t>
+          <t>According to PitchBook, Polymat was acquired by Tricon Energy on December 8, 2023.</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
@@ -2993,12 +2933,12 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Chemiplas Australia Pty Ltd</t>
+          <t>Protea Chemicals</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>https://chemiplas.com.au</t>
+          <t>proteachemicals.co.za</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -3008,17 +2948,13 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Azelis</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+          <t>Omnia Holdings</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>According to the company's 2023 Modern Slavery Statement, Azelis Pty Ltd acquired Chemiplas Australia Pty Ltd on March 31, 2023, while the company continued to operate as a separate entity.</t>
+          <t>Protea Chemicals continues to actively operate as a subsidiary under Omnia Holdings, which acquired the business to form its chemicals division.</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
@@ -3035,12 +2971,12 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Nexeo Plastics Mexico</t>
+          <t>OSP (acquired by Biesterfeld)</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>nexeoplastics.com</t>
+          <t>specialchem.com</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
@@ -3050,17 +2986,17 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>One Rock Capital Partners, LLC</t>
+          <t>Biesterfeld</t>
         </is>
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>An affiliate of One Rock Capital Partners completed the acquisition of Nexeo Plastics on March 29, 2019, according to an official One Rock Capital press release.</t>
+          <t>Biesterfeld announced that it acquired a majority stake in South Korean company OSP in May 2026, according to an official press release by Biesterfeld SE.</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
@@ -3077,12 +3013,12 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Megafarma (acquired by Azelis)</t>
+          <t>Azelis Korea</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>azelismexico.com</t>
+          <t>azelis.com</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -3097,54 +3033,54 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>According to the In-Cosmetics Korea directory, Azelis Korea Co., Ltd. was acquired by the Azelis Group in 2018.</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>medical_films_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Signet Excipients Pvt. Ltd. (acquired by IMCD)</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>signetexcipients.com</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>IMCD</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Azelis completed the acquisition of 100% of the outstanding shares of Megafarma on January 21, 2020, according to an official Azelis press release.</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="33" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>medical_films_verified_distributors</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Química Delta, S.A. de C.V. (acquired by Brenntag)</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>qdelta.com.mx</t>
-        </is>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>Brenntag</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Brenntag successfully closed the acquisition of the Mexican chemical distributor Química Delta on October 31, 2024, according to its Q3 2024 earnings transcript.</t>
+          <t>IMCD completed the acquisition of a 70% majority stake in Signet Excipients Pvt. Ltd. in 2020.</t>
         </is>
       </c>
       <c r="H63" s="9" t="inlineStr">
@@ -3161,12 +3097,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Univar Solutions Brasil Ltda</t>
+          <t>Al-Azzaz Chemicals Company</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>univarsolutions.com</t>
+          <t>https://www.brenntag.com</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3176,17 +3112,17 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Apollo Global Management</t>
+          <t>Brenntag</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Univar Solutions, the parent company of Univar Solutions Brasil Ltda, was acquired by Apollo Global Management in August 2023 according to Reuters.</t>
+          <t>Brenntag acquired a majority 75% stake in Al-Azzaz Chemicals in 2022, according to an official press release from Brenntag.</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -3203,37 +3139,37 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>IMCD Brasil</t>
+          <t>QuantiQ Distribuidora Ltda. (acquired by Caldic)</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>imcdgroup.com</t>
+          <t>caldic.com</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>absorbed</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>IMCD</t>
+          <t>Caldic</t>
         </is>
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>IMCD established its presence in Brazil by acquiring Makeni Chemicals in 2013, which serves as the platform for IMCD Brasil.</t>
+          <t>QuantiQ officially completed its rebranding and integration into the Caldic brand in January 2023 following Advent International's acquisition structures.</t>
         </is>
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3181,12 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Tecnomatiz Resinas (acquired by ALBIS)</t>
+          <t>Barentz Australia Pty Ltd</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>albis.com</t>
+          <t>barentz.com</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -3260,64 +3196,64 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>ALBIS Distribution GmbH &amp; Co. KG</t>
+          <t>Barentz</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Barentz completed the full acquisition of Additive Solutions (now rebranded as Barentz Australia) in December 2024, according to a press release from Barentz.</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>medical_films_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Química Anders</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>qanders.com</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Safic-Alcan</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>ALBIS acquired a majority stake in Tecnomatiz Resinas Ltda. in August 2025, but the company continues to operate independently under its own name according to an ALBIS press release.</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="33" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>medical_films_verified_distributors</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Suministro de Especialidades (acquired by Formerra)</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>https://suministro.com.mx</t>
-        </is>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>absorbed</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>Formerra</t>
-        </is>
-      </c>
-      <c r="F67" s="9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Suministro de Especialidades was strategically acquired by Formerra on November 7, 2023, according to Formerra's official press announcement.</t>
+          <t>Safic-Alcan acquired a majority stake in Química Anders in 2025 according to drymix.info.</t>
         </is>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -3329,12 +3265,12 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Tegral India Pvt. Ltd.</t>
+          <t>Chemiplas Australia Pty Ltd</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>vinmar.com</t>
+          <t>https://chemiplas.com.au</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -3344,17 +3280,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Vinmar</t>
+          <t>Azelis</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Tegral India Pvt. Ltd. announced it is part of the Vinmar family following its rebranding from Overseas Polymers Private Limited in 2024 according to LinkedIn.</t>
+          <t>According to the company's 2023 Modern Slavery Statement, Azelis Pty Ltd acquired Chemiplas Australia Pty Ltd on March 31, 2023, while the company continued to operate as a separate entity.</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -3371,37 +3307,37 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>D'Altomare Química</t>
+          <t>Nexeo Plastics Mexico</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>daltomare.com.br</t>
+          <t>nexeoplastics.com</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>absorbed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Univar Solutions</t>
+          <t>One Rock Capital Partners, LLC</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>Univar Inc. acquired specialty chemical distributor D'Altomare Química Ltda. in November 2014 and combined it with Univar's Brazil operations.</t>
+          <t>An affiliate of One Rock Capital Partners completed the acquisition of Nexeo Plastics on March 29, 2019, according to an official One Rock Capital press release.</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -3413,12 +3349,12 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Mulford Plastics</t>
+          <t>Megafarma (acquired by Azelis)</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>mulfordplastics.com</t>
+          <t>azelismexico.com</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -3428,17 +3364,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>PT Impack Pratama Industri Tbk</t>
+          <t>Azelis Group</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>According to a 2023 Forbes report, Impack acquired Mulford Plastics in 1990, gaining its distribution network in Australia and New Zealand.</t>
+          <t>Azelis completed the acquisition of 100% of the outstanding shares of Megafarma on January 21, 2020, according to an official Azelis press release.</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -3447,7 +3383,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="24" customHeight="1">
+    <row r="71" ht="33" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
           <t>medical_films_verified_distributors</t>
@@ -3455,12 +3391,12 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>ChemPoint EMEA</t>
+          <t>Química Delta, S.A. de C.V. (acquired by Brenntag)</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>chempoint.com</t>
+          <t>qdelta.com.mx</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
@@ -3470,17 +3406,17 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Univar Solutions</t>
+          <t>Brenntag</t>
         </is>
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>ChemPoint was acquired by Univar Solutions on July 16, 2015, according to its Tracxn company profile.</t>
+          <t>Brenntag successfully closed the acquisition of the Mexican chemical distributor Química Delta on October 31, 2024, according to its Q3 2024 earnings transcript.</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
@@ -3497,22 +3433,22 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>quantiQ Distribuidora Ltda (acquired by Caldic)</t>
+          <t>Univar Solutions Brasil Ltda</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>quantiq.com.br</t>
+          <t>univarsolutions.com</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>absorbed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Caldic</t>
+          <t>Apollo Global Management</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -3522,12 +3458,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>According to Caldic's official website, quantiQ was completely rebranded to the Caldic brand in January 2023 following its integration into Caldic Latin America.</t>
+          <t>Univar Solutions, the parent company of Univar Solutions Brasil Ltda, was acquired by Apollo Global Management in August 2023 according to Reuters.</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -3539,41 +3475,41 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Amco Polymers México</t>
+          <t>IMCD Brasil</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>amcopolymers.com.mx</t>
+          <t>imcdgroup.com</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>absorbed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Bamberger Amco Polymers</t>
+          <t>IMCD</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>Amco Polymers fully merged with Bamberger Polymers to form Bamberger Amco Polymers in March 2024, according to a press release from Bamberger Polymers.</t>
+          <t>IMCD established its presence in Brazil by acquiring Makeni Chemicals in 2013, which serves as the platform for IMCD Brasil.</t>
         </is>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>removed</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="24" customHeight="1">
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="33" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>medical_films_verified_distributors</t>
@@ -3581,12 +3517,12 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Hardie Polymers B.V.</t>
+          <t>Tecnomatiz Resinas (acquired by ALBIS)</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>https://www.hardiepolymers.eu</t>
+          <t>albis.com</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3596,17 +3532,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Nevis Capital</t>
+          <t>ALBIS Distribution GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Nevis Capital backed a management buyout of Hardie Polymers in November 2021, acquiring a majority stake.</t>
+          <t>ALBIS acquired a majority stake in Tecnomatiz Resinas Ltda. in August 2025, but the company continues to operate independently under its own name according to an ALBIS press release.</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
@@ -3623,37 +3559,37 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Barentz Switzerland AG</t>
+          <t>Suministro de Especialidades (acquired by Formerra)</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>barentz.com</t>
+          <t>https://suministro.com.mx</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>absorbed</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Barentz</t>
+          <t>Formerra</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>Barentz Switzerland AG has been fully integrated into the Barentz Group since 2024, as stated on Barentz's official Switzerland regional website.</t>
+          <t>Suministro de Especialidades was strategically acquired by Formerra on November 7, 2023, according to Formerra's official press announcement.</t>
         </is>
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3601,12 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Distrupol BV</t>
+          <t>Tegral India Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>https://www.distrupol.com</t>
+          <t>vinmar.com</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -3680,17 +3616,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Omya</t>
+          <t>Vinmar</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Same Distrupol group (distrupol.com) that Omya acquired in Feb 2025 and kept trading under the Distrupol brand.</t>
+          <t>Tegral India Pvt. Ltd. announced it is part of the Vinmar family following its rebranding from Overseas Polymers Private Limited in 2024 according to LinkedIn.</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
@@ -3707,37 +3643,37 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Pochteca Coremal</t>
+          <t>D'Altomare Química</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>brasilpochteca.net</t>
+          <t>daltomare.com.br</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>absorbed</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Grupo Pochteca</t>
+          <t>Univar Solutions</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>Coremal joined the Mexican international industrial distributor Grupo Pochteca via an acquisition in 2013, creating Pochteca Coremal.</t>
+          <t>Univar Inc. acquired specialty chemical distributor D'Altomare Química Ltda. in November 2014 and combined it with Univar's Brazil operations.</t>
         </is>
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3685,12 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>IMCD Mexico</t>
+          <t>Mulford Plastics</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>imcdmx.com</t>
+          <t>mulfordplastics.com</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -3764,17 +3700,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>IMCD</t>
+          <t>PT Impack Pratama Industri Tbk</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>IMCD entered the Mexican market through the acquisition of DCS Pharma in 2019, which was subsequently rebranded as IMCD Mexico in April 2020.</t>
+          <t>According to a 2023 Forbes report, Impack acquired Mulford Plastics in 1990, gaining its distribution network in Australia and New Zealand.</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
@@ -3783,7 +3719,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="33" customHeight="1">
+    <row r="79" ht="24" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
           <t>medical_films_verified_distributors</t>
@@ -3791,12 +3727,12 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>GME Chemicals (acquired by Biesterfeld Group)</t>
+          <t>ChemPoint EMEA</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>gmechem.com</t>
+          <t>chempoint.com</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -3806,17 +3742,17 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Biesterfeld Group</t>
+          <t>Univar Solutions</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>Biesterfeld Group completed the acquisition of a majority stake in Singapore-based GME Chemicals in October 2021, forming a joint venture while the company continues trading under its own name.</t>
+          <t>ChemPoint was acquired by Univar Solutions on July 16, 2015, according to its Tracxn company profile.</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
@@ -3825,7 +3761,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="24" customHeight="1">
+    <row r="80" ht="33" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>medical_films_verified_distributors</t>
@@ -3833,37 +3769,37 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Guztec Polymers Switzerland</t>
+          <t>quantiQ Distribuidora Ltda (acquired by Caldic)</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>https://guztecpolymers.com</t>
+          <t>quantiq.com.br</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>absorbed</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Hromatka Group</t>
+          <t>Caldic</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Guztec Polymers became part of the Hromatka Group in 2020 according to its official website.</t>
+          <t>According to Caldic's official website, quantiQ was completely rebranded to the Caldic brand in January 2023 following its integration into Caldic Latin America.</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -3875,41 +3811,41 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Solevo</t>
+          <t>Amco Polymers México</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>solevo.com</t>
+          <t>amcopolymers.com.mx</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>absorbed</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Development Partners International</t>
+          <t>Bamberger Amco Polymers</t>
         </is>
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>Solevo Group announced its acquisition by Development Partners International (DPI) in a deal that closed on April 18, 2023, according to an official statement on Solevo Group's website.</t>
+          <t>Amco Polymers fully merged with Bamberger Polymers to form Bamberger Amco Polymers in March 2024, according to a press release from Bamberger Polymers.</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="33" customHeight="1">
+          <t>removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="24" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>medical_films_verified_distributors</t>
@@ -3917,37 +3853,37 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>eXsource (acquired by Tricon Energy)</t>
+          <t>Hardie Polymers B.V.</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>exsource.com</t>
+          <t>https://www.hardiepolymers.eu</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>absorbed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Tricon Energy</t>
+          <t>Nevis Capital</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Tricon Energy acquired eXsource from Qenos in August 2024, integrating its business operations and workforce according to PitchBook and Argus Media.</t>
+          <t>Nevis Capital backed a management buyout of Hardie Polymers in November 2021, acquiring a majority stake.</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -3959,12 +3895,12 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>LifeHealthcare (acquired by EBOS Group)</t>
+          <t>Barentz Switzerland AG</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>lifehealthcare.com.au</t>
+          <t>barentz.com</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
@@ -3974,17 +3910,17 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>EBOS Group</t>
+          <t>Barentz</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>According to an official market announcement from EBOS Group, the acquisition of LifeHealthcare was completed on May 31, 2022.</t>
+          <t>Barentz Switzerland AG has been fully integrated into the Barentz Group since 2024, as stated on Barentz's official Switzerland regional website.</t>
         </is>
       </c>
       <c r="H83" s="9" t="inlineStr">
@@ -4001,12 +3937,12 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Manuchar NV</t>
+          <t>Distrupol BV</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>https://www.manuchar.com</t>
+          <t>https://www.distrupol.com</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -4016,17 +3952,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Lone Star Funds</t>
+          <t>Omya</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Manuchar NV was acquired by private equity firm Lone Star Funds in 2022, according to an official press release on Manuchar's website.</t>
+          <t>Same Distrupol group (distrupol.com) that Omya acquired in Feb 2025 and kept trading under the Distrupol brand.</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -4038,17 +3974,17 @@
     <row r="85" ht="33" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Healthcare 21 (UK) Ltd</t>
+          <t>Pochteca Coremal</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>healthcare21.eu</t>
+          <t>brasilpochteca.net</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
@@ -4058,17 +3994,17 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>AddLife AB Group</t>
+          <t>Grupo Pochteca</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>Healthcare 21 Group was acquired by the Swedish publicly listed MedTech company AddLife AB Group in April 2021.</t>
+          <t>Coremal joined the Mexican international industrial distributor Grupo Pochteca via an acquisition in 2013, creating Pochteca Coremal.</t>
         </is>
       </c>
       <c r="H85" s="9" t="inlineStr">
@@ -4080,17 +4016,17 @@
     <row r="86" ht="33" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Equity Medical Technologies</t>
+          <t>IMCD Mexico</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>equitymt.co.za</t>
+          <t>imcdmx.com</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -4100,11 +4036,19 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Clinigen South Africa</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
+          <t>IMCD</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>IMCD entered the Mexican market through the acquisition of DCS Pharma in 2019, which was subsequently rebranded as IMCD Mexico in April 2020.</t>
+        </is>
+      </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
           <t>renamed</t>
@@ -4114,17 +4058,17 @@
     <row r="87" ht="33" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>ORKYN'</t>
+          <t>GME Chemicals (acquired by Biesterfeld Group)</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>https://orkyn.fr</t>
+          <t>gmechem.com</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
@@ -4134,17 +4078,17 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>Homeperf</t>
+          <t>Biesterfeld Group</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>PitchBook reports that Orkyn's enteral nutrition business was acquired by Homeperf on January 16, 2026.</t>
+          <t>Biesterfeld Group completed the acquisition of a majority stake in Singapore-based GME Chemicals in October 2021, forming a joint venture while the company continues trading under its own name.</t>
         </is>
       </c>
       <c r="H87" s="9" t="inlineStr">
@@ -4153,20 +4097,20 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="33" customHeight="1">
+    <row r="88" ht="24" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>LVL Médical</t>
+          <t>Guztec Polymers Switzerland</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>https://lvlmedical.com</t>
+          <t>https://guztecpolymers.com</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -4176,17 +4120,17 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Air Liquide</t>
+          <t>Hromatka Group</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Air Liquide completed the acquisition of a controlling stake in LVL Médical Groupe SA in 2012, as reported by Air Liquide press materials.</t>
+          <t>Guztec Polymers became part of the Hromatka Group in 2020 according to its official website.</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
@@ -4198,17 +4142,17 @@
     <row r="89" ht="33" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>Homeperf (acquired by Sapio Group)</t>
+          <t>Solevo</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>https://homeperf.com</t>
+          <t>solevo.com</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
@@ -4218,17 +4162,17 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>Sapio Group</t>
+          <t>Development Partners International</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>Homeperf indicates on its official website that it has integrated into the Sapio Group.</t>
+          <t>Solevo Group announced its acquisition by Development Partners International (DPI) in a deal that closed on April 18, 2023, according to an official statement on Solevo Group's website.</t>
         </is>
       </c>
       <c r="H89" s="9" t="inlineStr">
@@ -4240,17 +4184,17 @@
     <row r="90" ht="33" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Mediq France</t>
+          <t>eXsource (acquired by Tricon Energy)</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>https://mediq.fr</t>
+          <t>exsource.com</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -4260,17 +4204,17 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Novomed Group</t>
+          <t>Tricon Energy</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Mediq France was acquired by Novomed Group in May 2017 and subsequently renamed NM Medical, according to Novomed Group's profile documentation.</t>
+          <t>Tricon Energy acquired eXsource from Qenos in August 2024, integrating its business operations and workforce according to PitchBook and Argus Media.</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
@@ -4282,59 +4226,59 @@
     <row r="91" ht="33" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>Alcura France</t>
+          <t>LifeHealthcare (acquired by EBOS Group)</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>https://alcura-health.fr</t>
+          <t>lifehealthcare.com.au</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>absorbed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Mutares SE &amp; Co. KGaA</t>
+          <t>EBOS Group</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>Mutares completed the acquisition of Alcura France on December 18, 2024, and subsequently carved out and rebranded the portfolio entity into Locapharm.</t>
+          <t>According to an official market announcement from EBOS Group, the acquisition of LifeHealthcare was completed on May 31, 2022.</t>
         </is>
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
     <row r="92" ht="33" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Asten Santé</t>
+          <t>Manuchar NV</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>https://astensante.fr</t>
+          <t>https://www.manuchar.com</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -4344,17 +4288,17 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>La Poste Groupe</t>
+          <t>Lone Star Funds</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Asten Santé was acquired by La Poste Groupe in 2017 according to a company profile on PitchBook.</t>
+          <t>Manuchar NV was acquired by private equity firm Lone Star Funds in 2022, according to an official press release on Manuchar's website.</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
@@ -4366,1042 +4310,858 @@
     <row r="93" ht="33" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>Aspironix s.r.o.</t>
+          <t>Distrupol (acquired by Omya)</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>https://www.aspironix.com</t>
+          <t>distrupol.com</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>Asker Healthcare Group</t>
-        </is>
-      </c>
-      <c r="F93" s="9" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr"/>
+      <c r="F93" s="9" t="inlineStr"/>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>Asker Healthcare Group acquired 100 percent of the shares in Aspironix on August 6, 2024, according to an official press release by Asker.</t>
+          <t>Same company as 'Distrupol BV (acquired by Omya)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="94" ht="33" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>DISTRIMED (acquired by Hygie31)</t>
+          <t>Al-Azzaz Chemicals Company (acquired by Brenntag)</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>https://www.distrimed.com</t>
+          <t>https://www.brenntag.com</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>Hygie31</t>
-        </is>
-      </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="5" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Hygie31 completed the acquisition of a majority 70% stake in Distrimed on December 4, 2023, from Bastide Le Confort Médical.</t>
+          <t>Same company as 'Al Azzaz Chemicals Company (acquired by Brenntag)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="33" customHeight="1">
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="24" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>Alliance Healthcare France</t>
+          <t>Plastribution</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>alliance-healthcare.fr</t>
+          <t>plastribution.co.uk</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>Cencora</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr"/>
+      <c r="F95" s="9" t="inlineStr"/>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>Alliance Healthcare (including its French entity) was acquired by Cencora (formerly AmerisourceBergen) from Walgreens Boots Alliance in 2021, as reported on Wikipedia.</t>
+          <t>Same company as 'Plastribution Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="96" ht="33" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Izasa Hospital, S.L.U. (acquired by Palex Medical)</t>
+          <t>Guzman Polymers, S.L. (acquired by Hromatka Group)</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>izasamedical.com</t>
+          <t>https://guzmanpolymers.es</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>Palex Medical</t>
-        </is>
-      </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="5" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>According to the Portuguese Competition Authority (Autoridade da Concorrência), Palex Medical, S.A.U. acquired exclusive control of Izasa Hospital, S.L.U. in May 2024.</t>
+          <t>Same company as 'Guzman Polymers S.L. (acquired by Hromatka Group)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="97" ht="33" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>MBA Incorporado, S.L.</t>
+          <t>Univar Solutions Brasil Ltda (acquired by Apollo Global Management)</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>https://mba.eu</t>
+          <t>univarsolutions.com</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>AddLife AB</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr"/>
+      <c r="F97" s="9" t="inlineStr"/>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>AddLife completed the 100% equity acquisition of MBA Incorporado S.L. on January 20, 2022, while continuing its operations as a separate subgroup.</t>
+          <t>Same company as 'Univar Solutions LLC (acquired by Apollo Global Management)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H97" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="33" customHeight="1">
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="24" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Nacil Médica 4 Group, S.L.</t>
+          <t>Safic-Alcan Brazil</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>https://medica4.com</t>
+          <t>https://www.safic-alcan.com/en-br/</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="F98" s="5" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>According to Einforma, Nacil Medica4 Group Sociedad Limitada entered liquidation and dissolution proceedings on February 3, 2026.</t>
+          <t>Same company as 'Safic-Alcan' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="99" ht="33" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>Palex Medical S.A.</t>
+          <t>Nexeo Plastics Europe</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>palexmedical.com</t>
+          <t>nexeoplastics.com</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>Apax Partners</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr"/>
+      <c r="F99" s="9" t="inlineStr"/>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>In December 2023, Apax Partners completed the acquisition of a co-controlling stake in Palex Medical alongside Fremman Capital.</t>
+          <t>Same company as 'Nexeo Plastics Spain S.L.U.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="33" customHeight="1">
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="24" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Prism Medical Products</t>
+          <t>PASCON SA</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>prism-medical.com</t>
+          <t>europages.co.uk</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>Henry Schein</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="5" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Henry Schein acquired a majority ownership interest in Prism Medical Products on January 5, 2021, according to Henry Schein's investor relations press release.</t>
+          <t>Same company as 'PASCON-SA' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="33" customHeight="1">
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="24" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>Twin Med, LLC</t>
+          <t>Vinmar Plastichem Mexico</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>https://www.twinmed.com</t>
+          <t>vinmar.com</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>Bison Capital Partners</t>
-        </is>
-      </c>
-      <c r="F101" s="9" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr"/>
+      <c r="F101" s="9" t="inlineStr"/>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>Twin Med, LLC was acquired via a recapitalization investment by Bison Capital Partners V, LP in late 2017, as stated in a Bison Capital press announcement.</t>
+          <t>Same company as 'Vinmar Plastichem México' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H101" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="33" customHeight="1">
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="24" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>SANIMED GmbH</t>
+          <t>AVH Polychem Private Limited</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>sanimed.de</t>
+          <t>https://avh.co.in/</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>HARTMANN / Palero Capital</t>
-        </is>
-      </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="5" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Palero Capital acquired Sanimed GmbH in March 2020 as reported by Preqin.</t>
+          <t>Same company as 'AVH Polychem' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="103" ht="33" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>Biomedica Italia S.r.l.</t>
+          <t>Ravago Shah Polymers</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>https://biomedica-italia.it</t>
+          <t>https://resinex.com</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>AddLife AB</t>
-        </is>
-      </c>
-      <c r="F103" s="9" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr"/>
+      <c r="F103" s="9" t="inlineStr"/>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>Biomedica Italia S.r.l. was established in December 2020 following its acquisition by AddLife AB, as noted in AddLife's corporate reports.</t>
+          <t>Same company as 'Ravago Shah Polymers Pvt. Ltd.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H103" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="104" ht="33" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Innovamedica S.p.A.</t>
+          <t>Barentz India</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>innovamedica.com</t>
+          <t>barentz.in</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>Gada Group</t>
-        </is>
-      </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="5" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Innovamedica S.p.A. was acquired by Gada Group on November 28, 2023, according to a press release by Palex Group.</t>
+          <t>Same company as 'Barentz India Private Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="105" ht="33" customHeight="1">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>Sangro medical service GmbH (acquired by Axcel)</t>
+          <t>Eventual Polychem Private Limited</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>sangro.de</t>
+          <t>http://sites.google.com/site/shivompolychemindia/</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>Axcel</t>
-        </is>
-      </c>
-      <c r="F105" s="9" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr"/>
+      <c r="F105" s="9" t="inlineStr"/>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>According to an Axcel annual review report, Axcel acquired sangro medical service GmbH in a carve-out deal completed on May 1, 2026, and operates it as an independent company.</t>
+          <t>Same company as 'Eventual PolyChem Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H105" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="33" customHeight="1">
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="24" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Dismed</t>
+          <t>Eventual Polychem Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>dismed.com</t>
+          <t>google.com</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>absorbed</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>FutureMed Healthcare Income Fund</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="5" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>According to a press release on Champlain Canada, Dismed Inc. was acquired by FutureMed Healthcare Income Fund on June 30, 2008, and its domain dismed.com is now for sale.</t>
+          <t>Same company as 'Eventual PolyChem Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>removed</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="33" customHeight="1">
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="24" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>GirodMedical</t>
+          <t>Grupo Pochteca, S.A.B. de C.V.</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>girodmedical.com</t>
+          <t>https://english.pochteca.net</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>absorbed</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>Hexamed</t>
-        </is>
-      </c>
-      <c r="F107" s="9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr"/>
+      <c r="F107" s="9" t="inlineStr"/>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>GirodMédical was legally integrated and merged into Hexamed Girod Médical SAS in July 2025, operating as a subsidiary of Hexamed, according to the official company profile.</t>
+          <t>Same company as 'Grupo Pochteca' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>removed</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="33" customHeight="1">
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="24" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Distri-Santé</t>
+          <t>Dajung Polymer Co., Ltd.</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>distrisante.fr</t>
+          <t>basf.com</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
+      <c r="F108" s="5" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>According to data from the official French directory Pappers, DISTRI SANTE SARL based in Toulouse was officially struck off and liquidated on September 27, 2006.</t>
+          <t>Same company as 'SamJung Polymer Co., Ltd.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>removed</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="33" customHeight="1">
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="24" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>Japan Medical Next Co., Ltd.</t>
+          <t>Pan Chemical Co., Ltd.</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>https://jmn.co.jp</t>
+          <t>http://panchemical.tradekorea.com</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>Mitsubishi Corporation</t>
-        </is>
-      </c>
-      <c r="F109" s="9" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr"/>
+      <c r="F109" s="9" t="inlineStr"/>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>Kobayashi Pharmaceutical fully transferred all shares of Japan Medical Next Co., Ltd. to Mitsubishi Corporation in 2012.</t>
+          <t>Same company as 'Pan Chemical' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="110" ht="33" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Healthcare 21 UK Ltd</t>
+          <t>Polymers International Ltd.</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>https://healthcare21.eu</t>
+          <t>polymers.co.nz</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>AddLife AB Group</t>
-        </is>
-      </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="5" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Healthcare 21 Group was acquired by the Swedish publicly listed MedTech company AddLife AB Group in April 2021.</t>
+          <t>Same company as 'Polymers International Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="33" customHeight="1">
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="24" customHeight="1">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>Somnotec (M) Sdn Bhd</t>
+          <t>Brenntag Australia Pty. Ltd.</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>somnotec.net</t>
+          <t>brenntag.com</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E111" s="6" t="inlineStr">
-        <is>
-          <t>Paragon Care Limited</t>
-        </is>
-      </c>
-      <c r="F111" s="9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr"/>
+      <c r="F111" s="9" t="inlineStr"/>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>On December 15, 2025, Paragon Care acquired 100% of the share capital of Somnotec (M) Sdn Bhd as part of the Somnotec Group acquisition.</t>
+          <t>Same company as 'Brenntag Australia Pty Ltd' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H111" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="112" ht="33" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
+          <t>medical_films_verified_distributors</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Izasa Hospital S.L.U. (acquired by Palex Medical)</t>
+          <t>Mais Polímeros do Brasil</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>https://izasahospital.com</t>
+          <t>maispolimeros.com.br</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>absorbed</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>Palex Medical</t>
-        </is>
-      </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="5" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Palex Medical's single shareholder approved the merger by absorption of Izasa Hospital S.L.U. in November 2025 according to BORME.</t>
+          <t>Same company as 'Mais Polímeros do Brasil Ltda' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
     <row r="113" ht="33" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
+          <t>medical_films_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>IMCD México</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>imcdmx.com</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr"/>
+      <c r="F113" s="9" t="inlineStr"/>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'IMCD Mexico (acquired by IMCD)' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="24" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>medical_films_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>Barentz Brasil</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>barentz.com</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="5" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'Barentz Brazil' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="24" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>medical_films_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>Química Anastacio</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>https://anastacio.com</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr"/>
+      <c r="F115" s="9" t="inlineStr"/>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'Química Anastácio' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="24" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>medical_films_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>SM Resinas Brasil Ltda.</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>smresinas.com</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="5" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'SM Resinas Brasil' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="33" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
           <t>negative_pressure_wound_therapy_verified_distributors</t>
         </is>
       </c>
-      <c r="B113" s="7" t="inlineStr">
-        <is>
-          <t>Burke &amp; Burke S.p.A.</t>
-        </is>
-      </c>
-      <c r="C113" s="8" t="inlineStr">
-        <is>
-          <t>https://burkeburke.com</t>
-        </is>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
-        <is>
-          <t>Palex Group</t>
-        </is>
-      </c>
-      <c r="F113" s="9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="G113" s="6" t="inlineStr">
-        <is>
-          <t>According to a company announcement, Palex Group completed the acquisition of 100% of Burke &amp; Burke S.p.A. in November 2023.</t>
-        </is>
-      </c>
-      <c r="H113" s="9" t="inlineStr">
-        <is>
-          <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="33" customHeight="1">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>Vital Medical Supplies</t>
-        </is>
-      </c>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>vitalmedicalsupplies.com.au</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>EBOS Group</t>
-        </is>
-      </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Vital Medical Supplies continues to operate under its own name following its acquisition by EBOS Group in 2006, according to records from PitchBook.</t>
-        </is>
-      </c>
-      <c r="H114" s="5" t="inlineStr">
-        <is>
-          <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="33" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
-        </is>
-      </c>
-      <c r="B115" s="7" t="inlineStr">
-        <is>
-          <t>Clifford Hallam Healthcare Pty Ltd</t>
-        </is>
-      </c>
-      <c r="C115" s="8" t="inlineStr">
-        <is>
-          <t>https://www.ch2.net.au</t>
-        </is>
-      </c>
-      <c r="D115" s="9" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>Paragon Care Limited</t>
-        </is>
-      </c>
-      <c r="F115" s="9" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="G115" s="6" t="inlineStr">
-        <is>
-          <t>Clifford Hallam Healthcare completed a transformative merger of equals with Paragon Care Limited in June 2024, according to a ParagonCare investor report.</t>
-        </is>
-      </c>
-      <c r="H115" s="9" t="inlineStr">
-        <is>
-          <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="33" customHeight="1">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>Regional Health Care Group</t>
-        </is>
-      </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>https://rhcg.com.au</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>Henry Schein</t>
-        </is>
-      </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Henry Schein announced the acquisition of Regional Health Care Group Pty Ltd (RHCG) in May 2023, according to a press release on its investor relations website.</t>
-        </is>
-      </c>
-      <c r="H116" s="5" t="inlineStr">
-        <is>
-          <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="46.5" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>negative_pressure_wound_therapy_verified_distributors</t>
-        </is>
-      </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>PartnerMed AB</t>
+          <t>Healthcare 21 (UK) Ltd</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>https://partnermed.se/</t>
+          <t>healthcare21.eu</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>absorbed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>Sanviva</t>
+          <t>AddLife AB Group</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>Nordic private equity firm Axcel simultaneously acquired four regional distributors including PartnerMed to establish the unified European distribution network Sanviva in June 2026, according to a report by Nelson Advisors.</t>
+          <t>Healthcare 21 Group was acquired by the Swedish publicly listed MedTech company AddLife AB Group in April 2021.</t>
         </is>
       </c>
       <c r="H117" s="9" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -5413,12 +5173,12 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>NDC, Inc.</t>
+          <t>Equity Medical Technologies</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>ndcinc.com</t>
+          <t>equitymt.co.za</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
@@ -5428,15 +5188,11 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Court Square Capital Partners</t>
+          <t>Clinigen South Africa</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>According to Court Square Capital Partners' portfolio profile, the private equity firm acquired National Distribution &amp; Contracting (NDC).</t>
-        </is>
-      </c>
+      <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="5" t="inlineStr">
         <is>
           <t>renamed</t>
@@ -5451,12 +5207,12 @@
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>Al Zahrawi Medical Supplies LLC</t>
+          <t>ORKYN'</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>zahrawigroup.com</t>
+          <t>https://orkyn.fr</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
@@ -5466,17 +5222,17 @@
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>ReAya Holding</t>
+          <t>Homeperf</t>
         </is>
       </c>
       <c r="F119" s="9" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>ReAya Holding joined the Zahrawi Group in 2013 and became the majority shareholder by 2016, though the group continues to trade actively under its own name.</t>
+          <t>PitchBook reports that Orkyn's enteral nutrition business was acquired by Homeperf on January 16, 2026.</t>
         </is>
       </c>
       <c r="H119" s="9" t="inlineStr">
@@ -5493,33 +5249,37 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Danica Pharma</t>
+          <t>LVL Médical</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>danicapharma.com</t>
+          <t>https://lvlmedical.com</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Air Liquide</t>
+        </is>
+      </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>According to a domain listing on Dovendi, the official domain danicapharma.com is currently up for sale, confirming the company has ceased trading.</t>
+          <t>Air Liquide completed the acquisition of a controlling stake in LVL Médical Groupe SA in 2012, as reported by Air Liquide press materials.</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -5531,12 +5291,12 @@
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>Fleetwood Healthcare</t>
+          <t>Homeperf (acquired by Sapio Group)</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>https://fleetwoodhealthcare.com</t>
+          <t>https://homeperf.com</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
@@ -5546,17 +5306,17 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>Hospital Services Ltd</t>
+          <t>Sapio Group</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>Hospital Services Ltd (HSL) successfully acquired Fleetwood Healthcare Ltd from KanDo Medical Ltd on August 15, 2023, according to a press release by KanDo Medical.</t>
+          <t>Homeperf indicates on its official website that it has integrated into the Sapio Group.</t>
         </is>
       </c>
       <c r="H121" s="9" t="inlineStr">
@@ -5573,37 +5333,37 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Accuscience Ireland Ltd</t>
+          <t>Mediq France</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>https://www.accuscience.ie</t>
+          <t>https://mediq.fr</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>absorbed</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Diploma PLC</t>
+          <t>Novomed Group</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Accuscience Ireland Ltd was acquired by UK-based Diploma PLC in May 2022, as reported by The Irish Independent.</t>
+          <t>Mediq France was acquired by Novomed Group in May 2017 and subsequently renamed NM Medical, according to Novomed Group's profile documentation.</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -5615,37 +5375,37 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>Celki VitalAire</t>
+          <t>Alcura France</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>celki.com</t>
+          <t>https://alcura-health.fr</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>absorbed</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>Air Liquide</t>
+          <t>Mutares SE &amp; Co. KGaA</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>Celki became part of the Air Liquide group via its home healthcare subsidiary VitalAire in 2007, according to the official website.</t>
+          <t>Mutares completed the acquisition of Alcura France on December 18, 2024, and subsequently carved out and rebranded the portfolio entity into Locapharm.</t>
         </is>
       </c>
       <c r="H123" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -5657,12 +5417,12 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Medshop Australia (acquired by Bunzl)</t>
+          <t>Asten Santé</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>medshop.com.au</t>
+          <t>https://astensante.fr</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
@@ -5672,17 +5432,17 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Bunzl plc</t>
+          <t>La Poste Groupe</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>According to the Bunzl Asia Pacific website, Bunzl plc acquired Medshop Australia in 2021.</t>
+          <t>Asten Santé was acquired by La Poste Groupe in 2017 according to a company profile on PitchBook.</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
@@ -5699,12 +5459,12 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>LMT Surgical (acquired by EBOS Group)</t>
+          <t>Aspironix s.r.o.</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>lmtsurgical.com</t>
+          <t>https://www.aspironix.com</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
@@ -5714,17 +5474,17 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>EBOS Group</t>
+          <t>Asker Healthcare Group</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>EBOS Group Limited acquired a 100% equity interest in LMT Surgical Pty Ltd on September 30, 2019, according to EBOS Group financial reports.</t>
+          <t>Asker Healthcare Group acquired 100 percent of the shares in Aspironix on August 6, 2024, according to an official press release by Asker.</t>
         </is>
       </c>
       <c r="H125" s="9" t="inlineStr">
@@ -5741,12 +5501,12 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Transmedic Group</t>
+          <t>DISTRIMED (acquired by Hygie31)</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>https://www.transmedicgroup.com</t>
+          <t>https://www.distrimed.com</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -5756,17 +5516,17 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>EBOS Group Ltd.</t>
+          <t>Hygie31</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>According to the Transmedic official website history page, the company was acquired by EBOS Group Ltd. in 2022.</t>
+          <t>Hygie31 completed the acquisition of a majority 70% stake in Distrimed on December 4, 2023, from Bastide Le Confort Médical.</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
@@ -5783,12 +5543,12 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>Yes Medical</t>
+          <t>Alliance Healthcare France</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>yesmed.com.au</t>
+          <t>alliance-healthcare.fr</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
@@ -5798,17 +5558,17 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>Yes Group</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>Yes Medical is active and merged into the trans-Tasman entity Yes Group in June 2024 while continuing to trade under its own regional name.</t>
+          <t>Alliance Healthcare (including its French entity) was acquired by Cencora (formerly AmerisourceBergen) from Walgreens Boots Alliance in 2021, as reported on Wikipedia.</t>
         </is>
       </c>
       <c r="H127" s="9" t="inlineStr">
@@ -5825,12 +5585,12 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>BMEC Pte. Ltd.</t>
+          <t>Izasa Hospital, S.L.U. (acquired by Palex Medical)</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>bmec.asia</t>
+          <t>izasamedical.com</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -5840,17 +5600,17 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Boustead Singapore Ltd</t>
+          <t>Palex Medical</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>BMEC Pte Ltd became part of Boustead Singapore Ltd following its acquisition of BMEC Holdings (formerly WhiteRock Incorporation) in 2018, as documented on Boustead Singapore's website.</t>
+          <t>According to the Portuguese Competition Authority (Autoridade da Concorrência), Palex Medical, S.A.U. acquired exclusive control of Izasa Hospital, S.L.U. in May 2024.</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
@@ -5867,12 +5627,12 @@
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>BMEC Malaysia</t>
+          <t>MBA Incorporado, S.L.</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>bmec.asia</t>
+          <t>https://mba.eu</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
@@ -5882,13 +5642,17 @@
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>Boustead Singapore Ltd</t>
-        </is>
-      </c>
-      <c r="F129" s="9" t="inlineStr"/>
+          <t>AddLife AB</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>BMEC Malaysia is active and listed as part of the BMEC Group owned by Boustead Singapore Ltd on its official website.</t>
+          <t>AddLife completed the 100% equity acquisition of MBA Incorporado S.L. on January 20, 2022, while continuing its operations as a separate subgroup.</t>
         </is>
       </c>
       <c r="H129" s="9" t="inlineStr">
@@ -5905,37 +5669,33 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Dupatri Hospitalar Comércio, Importação e Exportação Ltda (acquired by Grupo Elfa)</t>
+          <t>Nacil Médica 4 Group, S.L.</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>https://grupoelfa.com.br</t>
+          <t>https://medica4.com</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>Grupo Elfa</t>
-        </is>
-      </c>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>According to an official announcement by Grupo Elfa, they completed the full incorporation and acquisition of Dupatri Hospitalar in January 2021.</t>
+          <t>According to Einforma, Nacil Medica4 Group Sociedad Limitada entered liquidation and dissolution proceedings on February 3, 2026.</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -5947,42 +5707,1914 @@
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
+          <t>Palex Medical S.A.</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>palexmedical.com</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>Apax Partners</t>
+        </is>
+      </c>
+      <c r="F131" s="9" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>In December 2023, Apax Partners completed the acquisition of a co-controlling stake in Palex Medical alongside Fremman Capital.</t>
+        </is>
+      </c>
+      <c r="H131" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="33" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>Prism Medical Products</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>prism-medical.com</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Henry Schein</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Henry Schein acquired a majority ownership interest in Prism Medical Products on January 5, 2021, according to Henry Schein's investor relations press release.</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="33" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>Twin Med, LLC</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>https://www.twinmed.com</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>Bison Capital Partners</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>Twin Med, LLC was acquired via a recapitalization investment by Bison Capital Partners V, LP in late 2017, as stated in a Bison Capital press announcement.</t>
+        </is>
+      </c>
+      <c r="H133" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="33" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>SANIMED GmbH</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>sanimed.de</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>HARTMANN / Palero Capital</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Palero Capital acquired Sanimed GmbH in March 2020 as reported by Preqin.</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="33" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>Biomedica Italia S.r.l.</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>https://biomedica-italia.it</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>AddLife AB</t>
+        </is>
+      </c>
+      <c r="F135" s="9" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>Biomedica Italia S.r.l. was established in December 2020 following its acquisition by AddLife AB, as noted in AddLife's corporate reports.</t>
+        </is>
+      </c>
+      <c r="H135" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="33" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>Innovamedica S.p.A.</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>innovamedica.com</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Gada Group</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Innovamedica S.p.A. was acquired by Gada Group on November 28, 2023, according to a press release by Palex Group.</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="33" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>Sangro medical service GmbH (acquired by Axcel)</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>sangro.de</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>Axcel</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>According to an Axcel annual review report, Axcel acquired sangro medical service GmbH in a carve-out deal completed on May 1, 2026, and operates it as an independent company.</t>
+        </is>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="33" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>Dismed</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>dismed.com</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>absorbed</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>FutureMed Healthcare Income Fund</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>According to a press release on Champlain Canada, Dismed Inc. was acquired by FutureMed Healthcare Income Fund on June 30, 2008, and its domain dismed.com is now for sale.</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="33" customHeight="1">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>GirodMedical</t>
+        </is>
+      </c>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t>girodmedical.com</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>absorbed</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>Hexamed</t>
+        </is>
+      </c>
+      <c r="F139" s="9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>GirodMédical was legally integrated and merged into Hexamed Girod Médical SAS in July 2025, operating as a subsidiary of Hexamed, according to the official company profile.</t>
+        </is>
+      </c>
+      <c r="H139" s="9" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="33" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>Distri-Santé</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>distrisante.fr</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>According to data from the official French directory Pappers, DISTRI SANTE SARL based in Toulouse was officially struck off and liquidated on September 27, 2006.</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="33" customHeight="1">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>Japan Medical Next Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>https://jmn.co.jp</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>Mitsubishi Corporation</t>
+        </is>
+      </c>
+      <c r="F141" s="9" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>Kobayashi Pharmaceutical fully transferred all shares of Japan Medical Next Co., Ltd. to Mitsubishi Corporation in 2012.</t>
+        </is>
+      </c>
+      <c r="H141" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="33" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>Healthcare 21 UK Ltd</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>https://healthcare21.eu</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>AddLife AB Group</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare 21 Group was acquired by the Swedish publicly listed MedTech company AddLife AB Group in April 2021.</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="33" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>Somnotec (M) Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>somnotec.net</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>Paragon Care Limited</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>On December 15, 2025, Paragon Care acquired 100% of the share capital of Somnotec (M) Sdn Bhd as part of the Somnotec Group acquisition.</t>
+        </is>
+      </c>
+      <c r="H143" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="33" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>Izasa Hospital S.L.U. (acquired by Palex Medical)</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>https://izasahospital.com</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>absorbed</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Palex Medical</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Palex Medical's single shareholder approved the merger by absorption of Izasa Hospital S.L.U. in November 2025 according to BORME.</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="33" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>Burke &amp; Burke S.p.A.</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t>https://burkeburke.com</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>Palex Group</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>According to a company announcement, Palex Group completed the acquisition of 100% of Burke &amp; Burke S.p.A. in November 2023.</t>
+        </is>
+      </c>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="33" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>Vital Medical Supplies</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>vitalmedicalsupplies.com.au</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>EBOS Group</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Vital Medical Supplies continues to operate under its own name following its acquisition by EBOS Group in 2006, according to records from PitchBook.</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="33" customHeight="1">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>Clifford Hallam Healthcare Pty Ltd</t>
+        </is>
+      </c>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t>https://www.ch2.net.au</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>Paragon Care Limited</t>
+        </is>
+      </c>
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>Clifford Hallam Healthcare completed a transformative merger of equals with Paragon Care Limited in June 2024, according to a ParagonCare investor report.</t>
+        </is>
+      </c>
+      <c r="H147" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="33" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>Regional Health Care Group</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>https://rhcg.com.au</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Henry Schein</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Henry Schein announced the acquisition of Regional Health Care Group Pty Ltd (RHCG) in May 2023, according to a press release on its investor relations website.</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="46.5" customHeight="1">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>PartnerMed AB</t>
+        </is>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t>https://partnermed.se/</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>absorbed</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>Sanviva</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>Nordic private equity firm Axcel simultaneously acquired four regional distributors including PartnerMed to establish the unified European distribution network Sanviva in June 2026, according to a report by Nelson Advisors.</t>
+        </is>
+      </c>
+      <c r="H149" s="9" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="33" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>NDC, Inc.</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>ndcinc.com</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Court Square Capital Partners</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>According to Court Square Capital Partners' portfolio profile, the private equity firm acquired National Distribution &amp; Contracting (NDC).</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="33" customHeight="1">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>Al Zahrawi Medical Supplies LLC</t>
+        </is>
+      </c>
+      <c r="C151" s="8" t="inlineStr">
+        <is>
+          <t>zahrawigroup.com</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>ReAya Holding</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>ReAya Holding joined the Zahrawi Group in 2013 and became the majority shareholder by 2016, though the group continues to trade actively under its own name.</t>
+        </is>
+      </c>
+      <c r="H151" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="33" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>Danica Pharma</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>danicapharma.com</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr"/>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>According to a domain listing on Dovendi, the official domain danicapharma.com is currently up for sale, confirming the company has ceased trading.</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="33" customHeight="1">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t>Fleetwood Healthcare</t>
+        </is>
+      </c>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>https://fleetwoodhealthcare.com</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>Hospital Services Ltd</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>Hospital Services Ltd (HSL) successfully acquired Fleetwood Healthcare Ltd from KanDo Medical Ltd on August 15, 2023, according to a press release by KanDo Medical.</t>
+        </is>
+      </c>
+      <c r="H153" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="33" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>Accuscience Ireland Ltd</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>https://www.accuscience.ie</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Diploma PLC</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Accuscience Ireland Ltd was acquired by UK-based Diploma PLC in May 2022, as reported by The Irish Independent.</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="33" customHeight="1">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>Celki VitalAire</t>
+        </is>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t>celki.com</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>Air Liquide</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G155" s="6" t="inlineStr">
+        <is>
+          <t>Celki became part of the Air Liquide group via its home healthcare subsidiary VitalAire in 2007, according to the official website.</t>
+        </is>
+      </c>
+      <c r="H155" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="33" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>Medshop Australia (acquired by Bunzl)</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>medshop.com.au</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Bunzl plc</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>According to the Bunzl Asia Pacific website, Bunzl plc acquired Medshop Australia in 2021.</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="33" customHeight="1">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>LMT Surgical (acquired by EBOS Group)</t>
+        </is>
+      </c>
+      <c r="C157" s="8" t="inlineStr">
+        <is>
+          <t>lmtsurgical.com</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>EBOS Group</t>
+        </is>
+      </c>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>EBOS Group Limited acquired a 100% equity interest in LMT Surgical Pty Ltd on September 30, 2019, according to EBOS Group financial reports.</t>
+        </is>
+      </c>
+      <c r="H157" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="33" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>Transmedic Group</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>https://www.transmedicgroup.com</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>EBOS Group Ltd.</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>According to the Transmedic official website history page, the company was acquired by EBOS Group Ltd. in 2022.</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="33" customHeight="1">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>Yes Medical</t>
+        </is>
+      </c>
+      <c r="C159" s="8" t="inlineStr">
+        <is>
+          <t>yesmed.com.au</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>Yes Group</t>
+        </is>
+      </c>
+      <c r="F159" s="9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>Yes Medical is active and merged into the trans-Tasman entity Yes Group in June 2024 while continuing to trade under its own regional name.</t>
+        </is>
+      </c>
+      <c r="H159" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="33" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>BMEC Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>bmec.asia</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Boustead Singapore Ltd</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>BMEC Pte Ltd became part of Boustead Singapore Ltd following its acquisition of BMEC Holdings (formerly WhiteRock Incorporation) in 2018, as documented on Boustead Singapore's website.</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="33" customHeight="1">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>BMEC Malaysia</t>
+        </is>
+      </c>
+      <c r="C161" s="8" t="inlineStr">
+        <is>
+          <t>bmec.asia</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>Boustead Singapore Ltd</t>
+        </is>
+      </c>
+      <c r="F161" s="9" t="inlineStr"/>
+      <c r="G161" s="6" t="inlineStr">
+        <is>
+          <t>BMEC Malaysia is active and listed as part of the BMEC Group owned by Boustead Singapore Ltd on its official website.</t>
+        </is>
+      </c>
+      <c r="H161" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="33" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>Dupatri Hospitalar Comércio, Importação e Exportação Ltda (acquired by Grupo Elfa)</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>https://grupoelfa.com.br</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Grupo Elfa</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>According to an official announcement by Grupo Elfa, they completed the full incorporation and acquisition of Dupatri Hospitalar in January 2021.</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="33" customHeight="1">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
           <t>Biohosp Produtos Hospitalares S.A. (acquired by Grupo Elfa)</t>
         </is>
       </c>
-      <c r="C131" s="8" t="inlineStr">
+      <c r="C163" s="8" t="inlineStr">
         <is>
           <t>biohosp.com.br</t>
         </is>
       </c>
-      <c r="D131" s="9" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="D163" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
         <is>
           <t>Grupo Elfa</t>
         </is>
       </c>
-      <c r="F131" s="9" t="inlineStr">
+      <c r="F163" s="9" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="G131" s="6" t="inlineStr">
+      <c r="G163" s="6" t="inlineStr">
         <is>
           <t>According to an Elfa Medicamentos S.A. earnings release, the company acquired all shares of Biohosp on December 18, 2020.</t>
         </is>
       </c>
-      <c r="H131" s="9" t="inlineStr">
-        <is>
-          <t>renamed</t>
+      <c r="H163" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="33" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>Healthcare 21 UK Ltd (acquired by AddLife AB Group)</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>https://healthcare21.eu</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="5" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'Healthcare 21 (UK) Ltd (acquired by AddLife AB Group)' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="33" customHeight="1">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>Oxygen Care Limited</t>
+        </is>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t>oxygen-care.ie</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr"/>
+      <c r="F165" s="9" t="inlineStr"/>
+      <c r="G165" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'OxygenCare Ltd' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H165" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="33" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>NM Medical</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>nm-medical.fr</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr"/>
+      <c r="F166" s="5" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'NM Médical' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="33" customHeight="1">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>Oasis Dist SL</t>
+        </is>
+      </c>
+      <c r="C167" s="8" t="inlineStr">
+        <is>
+          <t>oasisdist.com</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr"/>
+      <c r="F167" s="9" t="inlineStr"/>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'Oasis Dist, S.L.' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H167" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="33" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>Palex Medical, S.A.</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>palexhealth.com</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" s="5" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'Palex Medical S.A. (acquired by Apax Partners)' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="33" customHeight="1">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>Suministros Hospitalarios S.A.</t>
+        </is>
+      </c>
+      <c r="C169" s="8" t="inlineStr">
+        <is>
+          <t>https://shmedical.com</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr"/>
+      <c r="F169" s="9" t="inlineStr"/>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'Suministros Hospitalarios, S.A.' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H169" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="33" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>MedEquip Depot</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>https://www.medequipdepot.com</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr"/>
+      <c r="F170" s="5" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'Medequip Depot, Inc.' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="33" customHeight="1">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>Globex Marketing &amp; Distribution Ltd.</t>
+        </is>
+      </c>
+      <c r="C171" s="8" t="inlineStr">
+        <is>
+          <t>globexbd.com</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr"/>
+      <c r="F171" s="9" t="inlineStr"/>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'Globex Marketing Company' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H171" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="33" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>Seçkinler Medikal A.Ş.</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>https://seckinlermedical.com</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr"/>
+      <c r="F172" s="5" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'Seçkinler Medikal' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="33" customHeight="1">
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>Med Surg Solutions</t>
+        </is>
+      </c>
+      <c r="C173" s="8" t="inlineStr">
+        <is>
+          <t>https://medsurgsolutions.com</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr"/>
+      <c r="F173" s="9" t="inlineStr"/>
+      <c r="G173" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'Med Surg Solutions MSS' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H173" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="33" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>H.N. Distributors</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>://indiamart.com</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr"/>
+      <c r="F174" s="5" t="inlineStr"/>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'Emsurg Healthcare (India) Private Limited' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="33" customHeight="1">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>Suizo Argentina</t>
+        </is>
+      </c>
+      <c r="C175" s="8" t="inlineStr">
+        <is>
+          <t>suizoargentina.com</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr"/>
+      <c r="F175" s="9" t="inlineStr"/>
+      <c r="G175" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'Suizo Argentina S.A.' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H175" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="33" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>Team Medical Supplies</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>teammed.com.au</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr"/>
+      <c r="F176" s="5" t="inlineStr"/>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'Team Medical' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="33" customHeight="1">
+      <c r="A177" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>KOVE Inc.</t>
+        </is>
+      </c>
+      <c r="C177" s="8" t="inlineStr">
+        <is>
+          <t>kovekorea.com</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="inlineStr"/>
+      <c r="F177" s="9" t="inlineStr"/>
+      <c r="G177" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'KOVE, Inc.' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H177" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="33" customHeight="1">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>YesMedical</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>yesmed.co.nz</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr"/>
+      <c r="F178" s="5" t="inlineStr"/>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'Yes Medical (acquired by Yes Group)' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H178" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="33" customHeight="1">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>negative_pressure_wound_therapy_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>C.R. Kennedy &amp; Company</t>
+        </is>
+      </c>
+      <c r="C179" s="8" t="inlineStr">
+        <is>
+          <t>crkennedy.com.au</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="inlineStr"/>
+      <c r="F179" s="9" t="inlineStr"/>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'C.R. Kennedy &amp; Company Pty Ltd' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H179" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H131"/>
+  <autoFilter ref="A1:H179"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -6114,6 +7746,54 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId178"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
